--- a/templates/GDA-FLC-027_gravedad_fino.xlsx
+++ b/templates/GDA-FLC-027_gravedad_fino.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeoDelta Líneas\Dropbox\14. GEODELTA\014 FORMATOS ACTUALIZADOS 2026\FORMATOS PARA DIGITAR ACTUALIZADOS 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DCM-04\AppData\Local\Temp\claude\D--Documents-Prototipos-claude-code-interfaz\dc24a8ee-ce81-4bc3-875e-fdda07eddd40\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23956B55-A307-43B7-A658-88C6C695C8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2113074-A2AA-4D66-8E06-D799441ADDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GUIA" sheetId="1" r:id="rId1"/>
@@ -2166,10 +2166,40 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2178,44 +2208,44 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2233,16 +2263,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2251,66 +2275,42 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2597,6 +2597,93 @@
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>73465</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>126561</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Firma Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F87823C0-629F-4C52-90DD-D061E19E706B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:srcRect l="88188"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7724775" y="8684065"/>
+          <a:ext cx="2533650" cy="996071"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>234251</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>480124</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Firma Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C8E2964-C650-4582-A7CC-3D304F942650}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11359451" y="8610600"/>
+          <a:ext cx="1941323" cy="1143000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2855,21 +2942,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="193"/>
-      <c r="B1" s="194"/>
-      <c r="C1" s="196" t="s">
+      <c r="A1" s="165"/>
+      <c r="B1" s="166"/>
+      <c r="C1" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="194"/>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="197" t="s">
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="198"/>
-      <c r="K1" s="199"/>
+      <c r="J1" s="172"/>
+      <c r="K1" s="173"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="2"/>
@@ -2899,31 +2986,31 @@
       <c r="AL1" s="3"/>
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
-      <c r="AO1" s="200" t="s">
+      <c r="AO1" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="AP1" s="167"/>
-      <c r="AQ1" s="167"/>
+      <c r="AP1" s="175"/>
+      <c r="AQ1" s="175"/>
       <c r="AR1" s="3"/>
       <c r="AS1" s="3"/>
       <c r="AT1" s="3"/>
     </row>
     <row r="2" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="180"/>
-      <c r="B2" s="179"/>
-      <c r="C2" s="201" t="s">
+      <c r="A2" s="167"/>
+      <c r="B2" s="151"/>
+      <c r="C2" s="176" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="179"/>
-      <c r="G2" s="179"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="202" t="s">
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="177" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="143"/>
-      <c r="K2" s="147"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="163"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
@@ -2961,19 +3048,19 @@
       <c r="AT2" s="3"/>
     </row>
     <row r="3" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="180"/>
-      <c r="B3" s="179"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="179"/>
-      <c r="I3" s="202" t="s">
+      <c r="A3" s="167"/>
+      <c r="B3" s="151"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="151"/>
+      <c r="I3" s="177" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="143"/>
-      <c r="K3" s="147"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="163"/>
       <c r="L3" s="1"/>
       <c r="M3" s="5" t="s">
         <v>6</v>
@@ -2997,12 +3084,12 @@
       <c r="AD3" s="3"/>
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
-      <c r="AG3" s="203" t="s">
+      <c r="AG3" s="178" t="s">
         <v>6</v>
       </c>
-      <c r="AH3" s="167"/>
-      <c r="AI3" s="167"/>
-      <c r="AJ3" s="167"/>
+      <c r="AH3" s="175"/>
+      <c r="AI3" s="175"/>
+      <c r="AJ3" s="175"/>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
@@ -3021,19 +3108,19 @@
       <c r="AT3" s="3"/>
     </row>
     <row r="4" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="195"/>
-      <c r="B4" s="149"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="149"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="205" t="s">
+      <c r="A4" s="168"/>
+      <c r="B4" s="169"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="169"/>
+      <c r="I4" s="180" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="206"/>
-      <c r="K4" s="207"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="181"/>
       <c r="L4" s="1"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -3055,10 +3142,10 @@
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
-      <c r="AG4" s="167"/>
-      <c r="AH4" s="167"/>
-      <c r="AI4" s="167"/>
-      <c r="AJ4" s="167"/>
+      <c r="AG4" s="175"/>
+      <c r="AH4" s="175"/>
+      <c r="AI4" s="175"/>
+      <c r="AJ4" s="175"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
@@ -3078,15 +3165,15 @@
     </row>
     <row r="5" spans="1:46" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="112"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="179"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="179"/>
-      <c r="F5" s="179"/>
-      <c r="G5" s="179"/>
-      <c r="H5" s="179"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
+      <c r="B5" s="179"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
       <c r="K5" s="113"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -3109,10 +3196,10 @@
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
-      <c r="AG5" s="167"/>
-      <c r="AH5" s="167"/>
-      <c r="AI5" s="167"/>
-      <c r="AJ5" s="167"/>
+      <c r="AG5" s="175"/>
+      <c r="AH5" s="175"/>
+      <c r="AI5" s="175"/>
+      <c r="AJ5" s="175"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
@@ -3135,17 +3222,17 @@
       <c r="B6" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="208"/>
-      <c r="D6" s="165"/>
-      <c r="E6" s="165"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="209" t="s">
+      <c r="C6" s="154"/>
+      <c r="D6" s="155"/>
+      <c r="E6" s="155"/>
+      <c r="F6" s="155"/>
+      <c r="G6" s="156" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="154"/>
-      <c r="I6" s="210"/>
-      <c r="J6" s="165"/>
-      <c r="K6" s="211"/>
+      <c r="H6" s="157"/>
+      <c r="I6" s="158"/>
+      <c r="J6" s="155"/>
+      <c r="K6" s="159"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="11" t="s">
@@ -3197,17 +3284,17 @@
       <c r="B7" s="116" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="142"/>
-      <c r="D7" s="143"/>
-      <c r="E7" s="143"/>
-      <c r="F7" s="143"/>
-      <c r="G7" s="144" t="s">
+      <c r="C7" s="164"/>
+      <c r="D7" s="146"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="146"/>
+      <c r="G7" s="160" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="145"/>
-      <c r="I7" s="146"/>
-      <c r="J7" s="143"/>
-      <c r="K7" s="147"/>
+      <c r="H7" s="161"/>
+      <c r="I7" s="162"/>
+      <c r="J7" s="146"/>
+      <c r="K7" s="163"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="11" t="s">
@@ -3259,17 +3346,17 @@
       <c r="B8" s="116" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="142"/>
-      <c r="D8" s="143"/>
-      <c r="E8" s="143"/>
-      <c r="F8" s="143"/>
-      <c r="G8" s="144" t="s">
+      <c r="C8" s="164"/>
+      <c r="D8" s="146"/>
+      <c r="E8" s="146"/>
+      <c r="F8" s="146"/>
+      <c r="G8" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="145"/>
-      <c r="I8" s="146"/>
-      <c r="J8" s="143"/>
-      <c r="K8" s="147"/>
+      <c r="H8" s="161"/>
+      <c r="I8" s="162"/>
+      <c r="J8" s="146"/>
+      <c r="K8" s="163"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1">
         <f>17-2.57</f>
@@ -3324,14 +3411,14 @@
       <c r="B9" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="142"/>
-      <c r="D9" s="143"/>
-      <c r="E9" s="143"/>
-      <c r="F9" s="143"/>
-      <c r="G9" s="144" t="s">
+      <c r="C9" s="164"/>
+      <c r="D9" s="146"/>
+      <c r="E9" s="146"/>
+      <c r="F9" s="146"/>
+      <c r="G9" s="160" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="145"/>
+      <c r="H9" s="161"/>
       <c r="I9" s="117" t="s">
         <v>22</v>
       </c>
@@ -3388,20 +3475,20 @@
       <c r="B10" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="142"/>
-      <c r="D10" s="143"/>
-      <c r="E10" s="143"/>
-      <c r="F10" s="143"/>
-      <c r="G10" s="156" t="s">
+      <c r="C10" s="164"/>
+      <c r="D10" s="146"/>
+      <c r="E10" s="146"/>
+      <c r="F10" s="146"/>
+      <c r="G10" s="214" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="157"/>
-      <c r="I10" s="142" t="str">
+      <c r="H10" s="215"/>
+      <c r="I10" s="164" t="str">
         <f>CONCATENATE(J9,," ",K9,D12,"-",B45,"-",F12)</f>
         <v xml:space="preserve"> --</v>
       </c>
-      <c r="J10" s="143"/>
-      <c r="K10" s="147"/>
+      <c r="J10" s="146"/>
+      <c r="K10" s="163"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="11" t="s">
@@ -3450,15 +3537,15 @@
     </row>
     <row r="11" spans="1:46" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="120"/>
-      <c r="B11" s="148"/>
-      <c r="C11" s="149"/>
-      <c r="D11" s="149"/>
-      <c r="E11" s="149"/>
-      <c r="F11" s="149"/>
-      <c r="G11" s="149"/>
-      <c r="H11" s="149"/>
-      <c r="I11" s="149"/>
-      <c r="J11" s="149"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="169"/>
+      <c r="D11" s="169"/>
+      <c r="E11" s="169"/>
+      <c r="F11" s="169"/>
+      <c r="G11" s="169"/>
+      <c r="H11" s="169"/>
+      <c r="I11" s="169"/>
+      <c r="J11" s="169"/>
       <c r="K11" s="121"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -3513,10 +3600,10 @@
         <v>28</v>
       </c>
       <c r="F12" s="17"/>
-      <c r="G12" s="158" t="s">
+      <c r="G12" s="216" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="154"/>
+      <c r="H12" s="157"/>
       <c r="I12" s="18"/>
       <c r="J12" s="19" t="s">
         <v>30</v>
@@ -3569,15 +3656,15 @@
       <c r="B13" s="116" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="142"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="143"/>
-      <c r="F13" s="143"/>
-      <c r="G13" s="143"/>
-      <c r="H13" s="143"/>
-      <c r="I13" s="143"/>
-      <c r="J13" s="143"/>
-      <c r="K13" s="147"/>
+      <c r="C13" s="164"/>
+      <c r="D13" s="146"/>
+      <c r="E13" s="146"/>
+      <c r="F13" s="146"/>
+      <c r="G13" s="146"/>
+      <c r="H13" s="146"/>
+      <c r="I13" s="146"/>
+      <c r="J13" s="146"/>
+      <c r="K13" s="163"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="11"/>
@@ -3729,19 +3816,19 @@
       <c r="AT15" s="3"/>
     </row>
     <row r="16" spans="1:46" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="150" t="s">
+      <c r="A16" s="211" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="151"/>
-      <c r="C16" s="151"/>
-      <c r="D16" s="151"/>
-      <c r="E16" s="151"/>
-      <c r="F16" s="151"/>
-      <c r="G16" s="151"/>
-      <c r="H16" s="151"/>
-      <c r="I16" s="151"/>
-      <c r="J16" s="151"/>
-      <c r="K16" s="152"/>
+      <c r="B16" s="207"/>
+      <c r="C16" s="207"/>
+      <c r="D16" s="207"/>
+      <c r="E16" s="207"/>
+      <c r="F16" s="207"/>
+      <c r="G16" s="207"/>
+      <c r="H16" s="207"/>
+      <c r="I16" s="207"/>
+      <c r="J16" s="207"/>
+      <c r="K16" s="212"/>
       <c r="L16" s="22"/>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -3841,13 +3928,13 @@
     <row r="18" spans="1:46" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="125"/>
       <c r="B18" s="126"/>
-      <c r="C18" s="153" t="s">
+      <c r="C18" s="199" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="154"/>
-      <c r="E18" s="154"/>
-      <c r="F18" s="154"/>
-      <c r="G18" s="155"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="213"/>
       <c r="H18" s="128"/>
       <c r="I18" s="128"/>
       <c r="J18" s="126"/>
@@ -3901,10 +3988,10 @@
     <row r="19" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="125"/>
       <c r="B19" s="126"/>
-      <c r="C19" s="159" t="s">
+      <c r="C19" s="205" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="160"/>
+      <c r="D19" s="202"/>
       <c r="E19" s="27" t="s">
         <v>36</v>
       </c>
@@ -4069,10 +4156,10 @@
     <row r="22" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="125"/>
       <c r="B22" s="126"/>
-      <c r="C22" s="161" t="s">
+      <c r="C22" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="162"/>
+      <c r="D22" s="144"/>
       <c r="E22" s="34" t="s">
         <v>43</v>
       </c>
@@ -4171,13 +4258,13 @@
     <row r="24" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="125"/>
       <c r="B24" s="126"/>
-      <c r="C24" s="163" t="s">
+      <c r="C24" s="206" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="151"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="164"/>
+      <c r="D24" s="207"/>
+      <c r="E24" s="207"/>
+      <c r="F24" s="207"/>
+      <c r="G24" s="208"/>
       <c r="H24" s="126"/>
       <c r="I24" s="126"/>
       <c r="J24" s="126"/>
@@ -4229,11 +4316,11 @@
     <row r="25" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="125"/>
       <c r="B25" s="126"/>
-      <c r="C25" s="159" t="s">
+      <c r="C25" s="205" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="165"/>
-      <c r="E25" s="160"/>
+      <c r="D25" s="155"/>
+      <c r="E25" s="202"/>
       <c r="F25" s="38"/>
       <c r="G25" s="39" t="e">
         <f>G19/(G20+G22-G21)</f>
@@ -4290,11 +4377,11 @@
     <row r="26" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="125"/>
       <c r="B26" s="126"/>
-      <c r="C26" s="212" t="s">
+      <c r="C26" s="145" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="143"/>
-      <c r="E26" s="213"/>
+      <c r="D26" s="146"/>
+      <c r="E26" s="147"/>
       <c r="F26" s="43"/>
       <c r="G26" s="44" t="e">
         <f>G22/(G20+G22-G21)</f>
@@ -4345,11 +4432,11 @@
     <row r="27" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="125"/>
       <c r="B27" s="126"/>
-      <c r="C27" s="212" t="s">
+      <c r="C27" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="143"/>
-      <c r="E27" s="213"/>
+      <c r="D27" s="146"/>
+      <c r="E27" s="147"/>
       <c r="F27" s="43"/>
       <c r="G27" s="44" t="e">
         <f>G19/(G20+G19-G21)</f>
@@ -4404,11 +4491,11 @@
     <row r="28" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="125"/>
       <c r="B28" s="126"/>
-      <c r="C28" s="212" t="s">
+      <c r="C28" s="145" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="143"/>
-      <c r="E28" s="213"/>
+      <c r="D28" s="146"/>
+      <c r="E28" s="147"/>
       <c r="F28" s="43" t="s">
         <v>51</v>
       </c>
@@ -4465,11 +4552,11 @@
     <row r="29" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="125"/>
       <c r="B29" s="126"/>
-      <c r="C29" s="212" t="s">
+      <c r="C29" s="145" t="s">
         <v>52</v>
       </c>
-      <c r="D29" s="143"/>
-      <c r="E29" s="213"/>
+      <c r="D29" s="146"/>
+      <c r="E29" s="147"/>
       <c r="F29" s="43" t="s">
         <v>53</v>
       </c>
@@ -4511,11 +4598,11 @@
     <row r="30" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="125"/>
       <c r="B30" s="126"/>
-      <c r="C30" s="212" t="s">
+      <c r="C30" s="145" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="143"/>
-      <c r="E30" s="213"/>
+      <c r="D30" s="146"/>
+      <c r="E30" s="147"/>
       <c r="F30" s="43" t="s">
         <v>55</v>
       </c>
@@ -4541,11 +4628,11 @@
       <c r="W30" s="23"/>
       <c r="X30" s="23"/>
       <c r="Y30" s="23"/>
-      <c r="Z30" s="212" t="s">
+      <c r="Z30" s="145" t="s">
         <v>56</v>
       </c>
-      <c r="AA30" s="214"/>
-      <c r="AB30" s="213"/>
+      <c r="AA30" s="148"/>
+      <c r="AB30" s="147"/>
       <c r="AC30" s="32" t="s">
         <v>57</v>
       </c>
@@ -4570,11 +4657,11 @@
     <row r="31" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="125"/>
       <c r="B31" s="126"/>
-      <c r="C31" s="215" t="s">
+      <c r="C31" s="149" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="206"/>
-      <c r="E31" s="162"/>
+      <c r="D31" s="143"/>
+      <c r="E31" s="144"/>
       <c r="F31" s="52" t="s">
         <v>59</v>
       </c>
@@ -4600,11 +4687,11 @@
       <c r="W31" s="23"/>
       <c r="X31" s="23"/>
       <c r="Y31" s="23"/>
-      <c r="Z31" s="212" t="s">
+      <c r="Z31" s="145" t="s">
         <v>60</v>
       </c>
-      <c r="AA31" s="214"/>
-      <c r="AB31" s="213"/>
+      <c r="AA31" s="148"/>
+      <c r="AB31" s="147"/>
       <c r="AC31" s="32" t="s">
         <v>37</v>
       </c>
@@ -4655,11 +4742,11 @@
       <c r="W32" s="23"/>
       <c r="X32" s="23"/>
       <c r="Y32" s="23"/>
-      <c r="Z32" s="212" t="s">
+      <c r="Z32" s="145" t="s">
         <v>61</v>
       </c>
-      <c r="AA32" s="214"/>
-      <c r="AB32" s="213"/>
+      <c r="AA32" s="148"/>
+      <c r="AB32" s="147"/>
       <c r="AC32" s="32" t="s">
         <v>37</v>
       </c>
@@ -4709,11 +4796,11 @@
       <c r="W33" s="59"/>
       <c r="X33" s="57"/>
       <c r="Y33" s="3"/>
-      <c r="Z33" s="212" t="s">
+      <c r="Z33" s="145" t="s">
         <v>63</v>
       </c>
-      <c r="AA33" s="214"/>
-      <c r="AB33" s="213"/>
+      <c r="AA33" s="148"/>
+      <c r="AB33" s="147"/>
       <c r="AC33" s="32" t="s">
         <v>64</v>
       </c>
@@ -4770,11 +4857,11 @@
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
-      <c r="Z34" s="212" t="s">
+      <c r="Z34" s="145" t="s">
         <v>65</v>
       </c>
-      <c r="AA34" s="214"/>
-      <c r="AB34" s="213"/>
+      <c r="AA34" s="148"/>
+      <c r="AB34" s="147"/>
       <c r="AC34" s="32" t="s">
         <v>66</v>
       </c>
@@ -4839,11 +4926,11 @@
       <c r="W35" s="61"/>
       <c r="X35" s="61"/>
       <c r="Y35" s="61"/>
-      <c r="Z35" s="212" t="s">
+      <c r="Z35" s="145" t="s">
         <v>70</v>
       </c>
-      <c r="AA35" s="214"/>
-      <c r="AB35" s="213"/>
+      <c r="AA35" s="148"/>
+      <c r="AB35" s="147"/>
       <c r="AC35" s="32" t="s">
         <v>71</v>
       </c>
@@ -4875,23 +4962,23 @@
       <c r="AT35" s="13"/>
     </row>
     <row r="36" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="216" t="s">
+      <c r="A36" s="150" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="179"/>
-      <c r="C36" s="179"/>
-      <c r="D36" s="179"/>
-      <c r="E36" s="179"/>
-      <c r="F36" s="183" t="s">
+      <c r="B36" s="151"/>
+      <c r="C36" s="151"/>
+      <c r="D36" s="151"/>
+      <c r="E36" s="151"/>
+      <c r="F36" s="152" t="s">
         <v>73</v>
       </c>
-      <c r="G36" s="179"/>
+      <c r="G36" s="151"/>
       <c r="H36" s="132"/>
-      <c r="I36" s="183" t="s">
+      <c r="I36" s="152" t="s">
         <v>74</v>
       </c>
-      <c r="J36" s="179"/>
-      <c r="K36" s="184"/>
+      <c r="J36" s="151"/>
+      <c r="K36" s="153"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="62" t="e">
@@ -4912,11 +4999,11 @@
       <c r="W36" s="61"/>
       <c r="X36" s="61"/>
       <c r="Y36" s="61"/>
-      <c r="Z36" s="161" t="s">
+      <c r="Z36" s="142" t="s">
         <v>75</v>
       </c>
-      <c r="AA36" s="206"/>
-      <c r="AB36" s="162"/>
+      <c r="AA36" s="143"/>
+      <c r="AB36" s="144"/>
       <c r="AC36" s="34" t="s">
         <v>59</v>
       </c>
@@ -4948,13 +5035,13 @@
       <c r="AT36" s="13"/>
     </row>
     <row r="37" spans="1:46" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="178" t="s">
+      <c r="A37" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="179"/>
-      <c r="C37" s="179"/>
-      <c r="D37" s="179"/>
-      <c r="E37" s="179"/>
+      <c r="B37" s="151"/>
+      <c r="C37" s="151"/>
+      <c r="D37" s="151"/>
+      <c r="E37" s="151"/>
       <c r="F37" s="134"/>
       <c r="G37" s="135"/>
       <c r="H37" s="132"/>
@@ -5007,11 +5094,11 @@
       <c r="AT37" s="13"/>
     </row>
     <row r="38" spans="1:46" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="180"/>
-      <c r="B38" s="179"/>
-      <c r="C38" s="179"/>
-      <c r="D38" s="179"/>
-      <c r="E38" s="179"/>
+      <c r="A38" s="167"/>
+      <c r="B38" s="151"/>
+      <c r="C38" s="151"/>
+      <c r="D38" s="151"/>
+      <c r="E38" s="151"/>
       <c r="F38" s="136"/>
       <c r="G38" s="132"/>
       <c r="H38" s="132"/>
@@ -5064,11 +5151,11 @@
       <c r="AT38" s="13"/>
     </row>
     <row r="39" spans="1:46" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="180"/>
-      <c r="B39" s="179"/>
-      <c r="C39" s="179"/>
-      <c r="D39" s="179"/>
-      <c r="E39" s="179"/>
+      <c r="A39" s="167"/>
+      <c r="B39" s="151"/>
+      <c r="C39" s="151"/>
+      <c r="D39" s="151"/>
+      <c r="E39" s="151"/>
       <c r="F39" s="136"/>
       <c r="G39" s="132"/>
       <c r="H39" s="132"/>
@@ -5122,11 +5209,11 @@
       <c r="AT39" s="23"/>
     </row>
     <row r="40" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="180"/>
-      <c r="B40" s="179"/>
-      <c r="C40" s="179"/>
-      <c r="D40" s="179"/>
-      <c r="E40" s="179"/>
+      <c r="A40" s="167"/>
+      <c r="B40" s="151"/>
+      <c r="C40" s="151"/>
+      <c r="D40" s="151"/>
+      <c r="E40" s="151"/>
       <c r="F40" s="136"/>
       <c r="G40" s="135"/>
       <c r="H40" s="137"/>
@@ -5180,21 +5267,21 @@
       <c r="AT40" s="13"/>
     </row>
     <row r="41" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="180"/>
-      <c r="B41" s="179"/>
-      <c r="C41" s="179"/>
-      <c r="D41" s="179"/>
-      <c r="E41" s="179"/>
-      <c r="F41" s="181" t="s">
+      <c r="A41" s="167"/>
+      <c r="B41" s="151"/>
+      <c r="C41" s="151"/>
+      <c r="D41" s="151"/>
+      <c r="E41" s="151"/>
+      <c r="F41" s="193" t="s">
         <v>79</v>
       </c>
-      <c r="G41" s="173"/>
+      <c r="G41" s="187"/>
       <c r="H41" s="137"/>
-      <c r="I41" s="181" t="s">
+      <c r="I41" s="193" t="s">
         <v>101</v>
       </c>
-      <c r="J41" s="173"/>
-      <c r="K41" s="182"/>
+      <c r="J41" s="187"/>
+      <c r="K41" s="194"/>
       <c r="L41" s="61"/>
       <c r="M41" s="61"/>
       <c r="N41" s="12"/>
@@ -5240,33 +5327,33 @@
       <c r="AT41" s="23"/>
     </row>
     <row r="42" spans="1:46" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="180"/>
-      <c r="B42" s="179"/>
-      <c r="C42" s="179"/>
-      <c r="D42" s="179"/>
-      <c r="E42" s="179"/>
-      <c r="F42" s="183" t="s">
+      <c r="A42" s="167"/>
+      <c r="B42" s="151"/>
+      <c r="C42" s="151"/>
+      <c r="D42" s="151"/>
+      <c r="E42" s="151"/>
+      <c r="F42" s="152" t="s">
         <v>81</v>
       </c>
-      <c r="G42" s="179"/>
+      <c r="G42" s="151"/>
       <c r="H42" s="132"/>
-      <c r="I42" s="183" t="s">
+      <c r="I42" s="152" t="s">
         <v>82</v>
       </c>
-      <c r="J42" s="179"/>
-      <c r="K42" s="184"/>
+      <c r="J42" s="151"/>
+      <c r="K42" s="153"/>
       <c r="L42" s="61"/>
       <c r="M42" s="61"/>
       <c r="N42" s="74">
         <f>N39/(N39-N40)</f>
         <v>1.5789473684210527</v>
       </c>
-      <c r="O42" s="166" t="s">
+      <c r="O42" s="209" t="s">
         <v>83</v>
       </c>
-      <c r="P42" s="167"/>
-      <c r="Q42" s="167"/>
-      <c r="R42" s="167"/>
+      <c r="P42" s="175"/>
+      <c r="Q42" s="175"/>
+      <c r="R42" s="175"/>
       <c r="S42" s="61"/>
       <c r="T42" s="61"/>
       <c r="U42" s="61"/>
@@ -5303,19 +5390,19 @@
       <c r="AT42" s="23"/>
     </row>
     <row r="43" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="185" t="s">
+      <c r="A43" s="195" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="186"/>
-      <c r="C43" s="186"/>
-      <c r="D43" s="186"/>
-      <c r="E43" s="186"/>
-      <c r="F43" s="186"/>
-      <c r="G43" s="186"/>
-      <c r="H43" s="186"/>
-      <c r="I43" s="186"/>
-      <c r="J43" s="186"/>
-      <c r="K43" s="187"/>
+      <c r="B43" s="196"/>
+      <c r="C43" s="196"/>
+      <c r="D43" s="196"/>
+      <c r="E43" s="196"/>
+      <c r="F43" s="196"/>
+      <c r="G43" s="196"/>
+      <c r="H43" s="196"/>
+      <c r="I43" s="196"/>
+      <c r="J43" s="196"/>
+      <c r="K43" s="197"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
@@ -5415,10 +5502,10 @@
     <row r="45" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="75"/>
-      <c r="C45" s="188" t="s">
+      <c r="C45" s="198" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="167"/>
+      <c r="D45" s="175"/>
       <c r="E45" s="75"/>
       <c r="F45" s="76" t="s">
         <v>86</v>
@@ -5473,8 +5560,8 @@
     <row r="46" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="22"/>
       <c r="B46" s="22"/>
-      <c r="C46" s="167"/>
-      <c r="D46" s="167"/>
+      <c r="C46" s="175"/>
+      <c r="D46" s="175"/>
       <c r="E46" s="77"/>
       <c r="F46" s="22"/>
       <c r="G46" s="22"/>
@@ -5527,8 +5614,8 @@
     <row r="47" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="22"/>
       <c r="B47" s="22"/>
-      <c r="C47" s="167"/>
-      <c r="D47" s="167"/>
+      <c r="C47" s="175"/>
+      <c r="D47" s="175"/>
       <c r="E47" s="77"/>
       <c r="F47" s="22"/>
       <c r="G47" s="22"/>
@@ -5581,8 +5668,8 @@
     <row r="48" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22"/>
       <c r="B48" s="22"/>
-      <c r="C48" s="167"/>
-      <c r="D48" s="167"/>
+      <c r="C48" s="175"/>
+      <c r="D48" s="175"/>
       <c r="E48" s="77"/>
       <c r="F48" s="22"/>
       <c r="G48" s="22"/>
@@ -5635,8 +5722,8 @@
     <row r="49" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="22"/>
       <c r="B49" s="22"/>
-      <c r="C49" s="167"/>
-      <c r="D49" s="167"/>
+      <c r="C49" s="175"/>
+      <c r="D49" s="175"/>
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
       <c r="G49" s="22"/>
@@ -5689,8 +5776,8 @@
     <row r="50" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="22"/>
       <c r="B50" s="22"/>
-      <c r="C50" s="167"/>
-      <c r="D50" s="167"/>
+      <c r="C50" s="175"/>
+      <c r="D50" s="175"/>
       <c r="E50" s="22"/>
       <c r="F50" s="22"/>
       <c r="G50" s="22"/>
@@ -5807,13 +5894,13 @@
       <c r="J52" s="22"/>
       <c r="K52" s="22"/>
       <c r="L52" s="22"/>
-      <c r="M52" s="153" t="s">
+      <c r="M52" s="199" t="s">
         <v>87</v>
       </c>
-      <c r="N52" s="154"/>
-      <c r="O52" s="154"/>
-      <c r="P52" s="154"/>
-      <c r="Q52" s="189"/>
+      <c r="N52" s="157"/>
+      <c r="O52" s="157"/>
+      <c r="P52" s="157"/>
+      <c r="Q52" s="200"/>
       <c r="R52" s="23"/>
       <c r="S52" s="23"/>
       <c r="T52" s="23"/>
@@ -5866,14 +5953,14 @@
       <c r="M53" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="N53" s="190" t="s">
+      <c r="N53" s="201" t="s">
         <v>89</v>
       </c>
-      <c r="O53" s="160"/>
-      <c r="P53" s="190" t="s">
+      <c r="O53" s="202"/>
+      <c r="P53" s="201" t="s">
         <v>90</v>
       </c>
-      <c r="Q53" s="191"/>
+      <c r="Q53" s="203"/>
       <c r="R53" s="23"/>
       <c r="S53" s="23"/>
       <c r="T53" s="23"/>
@@ -5926,13 +6013,13 @@
       <c r="M54" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="N54" s="192"/>
-      <c r="O54" s="169"/>
-      <c r="P54" s="192">
+      <c r="N54" s="204"/>
+      <c r="O54" s="183"/>
+      <c r="P54" s="204">
         <f>100-N54</f>
         <v>100</v>
       </c>
-      <c r="Q54" s="174"/>
+      <c r="Q54" s="188"/>
       <c r="R54" s="23"/>
       <c r="S54" s="23"/>
       <c r="T54" s="23"/>
@@ -5982,15 +6069,15 @@
       <c r="J55" s="22"/>
       <c r="K55" s="22"/>
       <c r="L55" s="22"/>
-      <c r="M55" s="168" t="s">
+      <c r="M55" s="182" t="s">
         <v>91</v>
       </c>
-      <c r="N55" s="169"/>
-      <c r="O55" s="172" t="s">
+      <c r="N55" s="183"/>
+      <c r="O55" s="186" t="s">
         <v>92</v>
       </c>
-      <c r="P55" s="173"/>
-      <c r="Q55" s="174"/>
+      <c r="P55" s="187"/>
+      <c r="Q55" s="188"/>
       <c r="R55" s="23"/>
       <c r="S55" s="23"/>
       <c r="T55" s="23"/>
@@ -6040,11 +6127,11 @@
       <c r="J56" s="22"/>
       <c r="K56" s="22"/>
       <c r="L56" s="22"/>
-      <c r="M56" s="170"/>
-      <c r="N56" s="171"/>
-      <c r="O56" s="175"/>
-      <c r="P56" s="176"/>
-      <c r="Q56" s="177"/>
+      <c r="M56" s="184"/>
+      <c r="N56" s="185"/>
+      <c r="O56" s="189"/>
+      <c r="P56" s="190"/>
+      <c r="Q56" s="191"/>
       <c r="R56" s="23"/>
       <c r="S56" s="23"/>
       <c r="T56" s="23"/>
@@ -52364,6 +52451,54 @@
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="O42:R42"/>
+    <mergeCell ref="M55:N56"/>
+    <mergeCell ref="O55:Q56"/>
+    <mergeCell ref="A37:E42"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="C45:D50"/>
+    <mergeCell ref="M52:Q52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="AO1:AQ1"/>
+    <mergeCell ref="C2:H4"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="AG3:AJ5"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="C7:F7"/>
     <mergeCell ref="Z36:AB36"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C27:E27"/>
@@ -52380,54 +52515,6 @@
     <mergeCell ref="Z33:AB33"/>
     <mergeCell ref="Z34:AB34"/>
     <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="AO1:AQ1"/>
-    <mergeCell ref="C2:H4"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="AG3:AJ5"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="M55:N56"/>
-    <mergeCell ref="O55:Q56"/>
-    <mergeCell ref="A37:E42"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="C45:D50"/>
-    <mergeCell ref="M52:Q52"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="O42:R42"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="G9:H9"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:D12 G19:G22 AD30:AD32 M54:N54 P54">
     <cfRule type="containsBlanks" dxfId="6" priority="2">
